--- a/F3M_FP&A_assessment_ready_AI_v1.xlsx
+++ b/F3M_FP&A_assessment_ready_AI_v1.xlsx
@@ -987,7 +987,7 @@
     <t>1.1-1.4</t>
   </si>
   <si>
-    <t>Develop guided workflows for creating budgets; On demand forecasting and scenario modeling; AI-supported budget allocation</t>
+    <t>Desarrollo de flujos guiados para la elaboración de presupuestos; Previsión y modelización de escenarios bajo demanda; Asignación presupuestaria asistida por IA</t>
   </si>
   <si>
     <t>Planificación driver-based, rolling forecast, escenarios automatizados y workflows colaborativos</t>
@@ -999,7 +999,7 @@
     <t>2.1-2.4</t>
   </si>
   <si>
-    <t>Mgmt Reporting Actuals Plan Variance + Commentary; Generate account variance analysis and intelligent explanations; FinanceAI Insights Platform</t>
+    <t>Informes de gestión con real, plan, desviación y comentario; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes; FinanceAI Insights Platform</t>
   </si>
   <si>
     <t>Reporting automatizado con commentary, insights, alertas y explicación de desviaciones</t>
@@ -1008,7 +1008,7 @@
     <t>3.1-3.4</t>
   </si>
   <si>
-    <t>Summarize and score project proposals; Project-level recommendations</t>
+    <t>Resumen y puntuación de propuestas de proyecto; Recomendaciones a nivel de proyecto</t>
   </si>
   <si>
     <t>Scoring de iniciativas, priorización dinámica y seguimiento de beneficios</t>
@@ -1017,7 +1017,7 @@
     <t>4.1-4.4</t>
   </si>
   <si>
-    <t>Perform analysis and investigation and provide insights on demand; Data access for all; Enterprise-wide data search and access</t>
+    <t>Realización de análisis e investigación con conclusiones bajo demanda; Acceso a datos para toda la organización; Búsqueda y acceso a datos en toda la compañía</t>
   </si>
   <si>
     <t>Decision intelligence, insights predictivos y autoservicio gobernado</t>
@@ -1026,7 +1026,7 @@
     <t>5.1-5.4</t>
   </si>
   <si>
-    <t>Generate investing strategies; Identify patterns to predict future financial performance; Integrated business planning</t>
+    <t>Generación de estrategias de inversión; Identificación de patrones para predecir el rendimiento financiero futuro; Planificación integrada de negocio</t>
   </si>
   <si>
     <t>Planificación estratégica continua, simulación avanzada y asignación dinámica de recursos</t>

--- a/F3M_FP&A_assessment_ready_AI_v1.xlsx
+++ b/F3M_FP&A_assessment_ready_AI_v1.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="351">
   <si>
     <t>Capacidad</t>
   </si>
@@ -1045,6 +1045,123 @@
   </si>
   <si>
     <t>- Accountability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrollo de flujos guiados para la elaboración de presupuestos; Previsión y modelización de escenarios bajo demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA guía el calendario presupuestario, detecta retrasos y dependencias entre áreas y propone la replanificación cuando cambian los supuestos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrollo de flujos guiados para la elaboración de presupuestos; Asignación presupuestaria asistida por IA; Identificación de patrones para predecir el rendimiento financiero futuro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA identifica los drivers que mejor explican el resultado, propone sus valores de partida y cuantifica la sensibilidad de cada uno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previsión y modelización de escenarios bajo demanda; Identificación de patrones para predecir el rendimiento financiero futuro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA genera el forecast de forma continua, construye escenarios alternativos bajo demanda y alerta cuando la desviación esperada supera el umbral.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrollo de flujos guiados para la elaboración de presupuestos; FinanceAI Insights Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA guía la aportación de cada responsable, valida su coherencia con los drivers acordados y da seguimiento a los compromisos adquiridos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informes de gestión con real, plan, desviación y comentario; FinanceAI Insights Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA produce el informe de gestión con la desviación calculada y el comentario redactado, y ajusta el nivel de detalle a cada destinatario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de análisis de desviaciones de cuentas con explicaciones inteligentes; Identificación de patrones para predecir el rendimiento financiero futuro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA descompone la desviación por driver, identifica la causa raíz y anticipa si la brecha se va a cerrar o a ampliar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinanceAI Insights Platform; Búsqueda y acceso a datos en toda la compañía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA acompaña el cuadro de mando con conclusiones automáticas, alertas y respuesta a preguntas en lenguaje natural sobre el propio dato.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informes de gestión con real, plan, desviación y comentario; Recomendaciones a nivel de proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA prepara la reunión de seguimiento con las desviaciones relevantes, las acciones pendientes y una recomendación priorizada para cada una.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumen y puntuación de propuestas de proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA revisa que cada business case cumpla la plantilla corporativa, resume su propuesta y señala los supuestos que quedan sin justificar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previsión y modelización de escenarios bajo demanda; Resumen y puntuación de propuestas de proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA construye los escenarios del business case, prueba la sensibilidad de los supuestos y compara el modelo con iniciativas anteriores comparables.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumen y puntuación de propuestas de proyecto; Asignación presupuestaria asistida por IA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA puntúa y ordena la cartera de iniciativas por valor ajustado a riesgo y propone cómo repartir el capital disponible entre ellas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendaciones a nivel de proyecto; Identificación de patrones para predecir el rendimiento financiero futuro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA compara el beneficio real con el comprometido, explica la diferencia y devuelve el aprendizaje a los supuestos de los siguientes business cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Búsqueda y acceso a datos en toda la compañía; Realización de análisis e investigación con conclusiones bajo demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA localiza el dato en cualquier sistema, indica de qué fuente oficial procede y responde en lenguaje natural sobre la cifra que sustenta la decisión.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA simula el impacto financiero de cada alternativa, estima su probabilidad y recomienda la opción con mejor relación entre valor y riesgo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realización de análisis e investigación con conclusiones bajo demanda; Acceso a datos para toda la organización</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA prepara el contraste con negocio: reúne la evidencia, cuestiona los supuestos optimistas y propone las preguntas que conviene plantear.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de análisis de desviaciones de cuentas con explicaciones inteligentes; FinanceAI Insights Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA redacta el mensaje ejecutivo a partir de las cifras: drivers, riesgos, decisiones que se piden y acciones propuestas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de estrategias de inversión; Planificación integrada de negocio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA proyecta el plan plurianual sobre drivers estratégicos, lo actualiza con señales de mercado y propone dónde asignar los recursos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previsión y modelización de escenarios bajo demanda; Generación de estrategias de inversión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA simula escenarios disruptivos, cuantifica su impacto en resultado, caja y solvencia, y propone el plan de contingencia asociado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificación integrada de negocio; Recomendaciones a nivel de proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA conecta objetivos estratégicos, presupuesto e iniciativas, detecta dónde se rompe la cadena y propone la reasignación de recursos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificación de patrones para predecir el rendimiento financiero futuro; Generación de estrategias de inversión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA mide la creación de valor de cada plan, la anticipa con indicadores adelantados y recomienda reasignar capital antes de que se deteriore.</t>
   </si>
 </sst>
 </file>
@@ -5130,7 +5247,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -5162,13 +5279,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="D2" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="E2" t="s">
         <v>294</v>
@@ -5176,16 +5293,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>295</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="D3" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="E3" t="s">
         <v>294</v>
@@ -5193,16 +5310,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="D4" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="E4" t="s">
         <v>294</v>
@@ -5210,16 +5327,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>301</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="D5" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="E5" t="s">
         <v>294</v>
@@ -5227,18 +5344,273 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>322</v>
+      </c>
+      <c r="D7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
+        <v>324</v>
+      </c>
+      <c r="D8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>326</v>
+      </c>
+      <c r="D9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D10" t="s">
+        <v>329</v>
+      </c>
+      <c r="E10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D11" t="s">
+        <v>331</v>
+      </c>
+      <c r="E11" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" t="s">
+        <v>332</v>
+      </c>
+      <c r="D12" t="s">
+        <v>333</v>
+      </c>
+      <c r="E12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s">
+        <v>334</v>
+      </c>
+      <c r="D13" t="s">
+        <v>335</v>
+      </c>
+      <c r="E13" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>336</v>
+      </c>
+      <c r="D14" t="s">
+        <v>337</v>
+      </c>
+      <c r="E14" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" t="s">
+        <v>316</v>
+      </c>
+      <c r="D15" t="s">
+        <v>338</v>
+      </c>
+      <c r="E15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" t="s">
+        <v>339</v>
+      </c>
+      <c r="D16" t="s">
+        <v>340</v>
+      </c>
+      <c r="E16" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" t="s">
+        <v>341</v>
+      </c>
+      <c r="D17" t="s">
+        <v>342</v>
+      </c>
+      <c r="E17" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>183</v>
       </c>
-      <c r="B6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C6" t="s">
-        <v>305</v>
-      </c>
-      <c r="D6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="B18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" t="s">
+        <v>343</v>
+      </c>
+      <c r="D18" t="s">
+        <v>344</v>
+      </c>
+      <c r="E18" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" t="s">
+        <v>345</v>
+      </c>
+      <c r="D19" t="s">
+        <v>346</v>
+      </c>
+      <c r="E19" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" t="s">
+        <v>347</v>
+      </c>
+      <c r="D20" t="s">
+        <v>348</v>
+      </c>
+      <c r="E20" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B21" t="s">
+        <v>214</v>
+      </c>
+      <c r="C21" t="s">
+        <v>349</v>
+      </c>
+      <c r="D21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E21" t="s">
         <v>294</v>
       </c>
     </row>

--- a/F3M_FP&A_assessment_ready_AI_v1.xlsx
+++ b/F3M_FP&A_assessment_ready_AI_v1.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="370">
   <si>
     <t>Capacidad</t>
   </si>
@@ -1162,6 +1162,63 @@
   </si>
   <si>
     <t xml:space="preserve">IA mide la creación de valor de cada plan, la anticipa con indicadores adelantados y recomienda reasignar capital antes de que se deteriore.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flujos guiados de elaboración presupuestaria; Previsión y escenarios bajo demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flujos guiados de elaboración presupuestaria; Asignación presupuestaria asistida por IA; Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previsión y escenarios bajo demanda; Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flujos guiados de elaboración presupuestaria; Analista digital de Finanzas bajo demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informes de gestión con comentario automático; Analista digital de Finanzas bajo demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis de desviaciones con explicación automática; Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista digital de Finanzas bajo demanda; Consulta del dato en lenguaje natural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informes de gestión con comentario automático; Recomendaciones de acción a nivel de proyecto; Reporting estandarizado de revisión de desempeño</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumen y puntuación de propuestas de inversión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previsión y escenarios bajo demanda; Resumen y puntuación de propuestas de inversión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumen y puntuación de propuestas de inversión; Asignación presupuestaria asistida por IA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendaciones de acción a nivel de proyecto; Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consulta del dato en lenguaje natural; Analista digital de Finanzas bajo demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previsión y escenarios bajo demanda; Patrones históricos para predecir el rendimiento; Modelos retadores para contrastar escenarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis de desviaciones con explicación automática; Analista digital de Finanzas bajo demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previsión y escenarios bajo demanda; Generación de estrategias de inversión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificación integrada de negocio; Recomendaciones de acción a nivel de proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrones históricos para predecir el rendimiento; Generación de estrategias de inversión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumen y puntuación de propuestas de inversión; Recomendaciones de acción a nivel de proyecto</t>
   </si>
 </sst>
 </file>
@@ -5282,7 +5339,7 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>312</v>
+        <v>351</v>
       </c>
       <c r="D2" t="s">
         <v>313</v>
@@ -5299,7 +5356,7 @@
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="D3" t="s">
         <v>315</v>
@@ -5316,7 +5373,7 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="D4" t="s">
         <v>317</v>
@@ -5333,7 +5390,7 @@
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="D5" t="s">
         <v>319</v>
@@ -5350,7 +5407,7 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>320</v>
+        <v>355</v>
       </c>
       <c r="D6" t="s">
         <v>321</v>
@@ -5367,7 +5424,7 @@
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="D7" t="s">
         <v>323</v>
@@ -5384,7 +5441,7 @@
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>324</v>
+        <v>357</v>
       </c>
       <c r="D8" t="s">
         <v>325</v>
@@ -5401,7 +5458,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="D9" t="s">
         <v>327</v>
@@ -5418,7 +5475,7 @@
         <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="D10" t="s">
         <v>329</v>
@@ -5435,7 +5492,7 @@
         <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="D11" t="s">
         <v>331</v>
@@ -5452,7 +5509,7 @@
         <v>122</v>
       </c>
       <c r="C12" t="s">
-        <v>332</v>
+        <v>361</v>
       </c>
       <c r="D12" t="s">
         <v>333</v>
@@ -5469,7 +5526,7 @@
         <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="D13" t="s">
         <v>335</v>
@@ -5486,7 +5543,7 @@
         <v>143</v>
       </c>
       <c r="C14" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="D14" t="s">
         <v>337</v>
@@ -5503,7 +5560,7 @@
         <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>316</v>
+        <v>364</v>
       </c>
       <c r="D15" t="s">
         <v>338</v>
@@ -5520,7 +5577,7 @@
         <v>163</v>
       </c>
       <c r="C16" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="D16" t="s">
         <v>340</v>
@@ -5537,7 +5594,7 @@
         <v>173</v>
       </c>
       <c r="C17" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="D17" t="s">
         <v>342</v>
@@ -5571,7 +5628,7 @@
         <v>194</v>
       </c>
       <c r="C19" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="D19" t="s">
         <v>346</v>
@@ -5588,7 +5645,7 @@
         <v>204</v>
       </c>
       <c r="C20" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="D20" t="s">
         <v>348</v>
@@ -5605,7 +5662,7 @@
         <v>214</v>
       </c>
       <c r="C21" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="D21" t="s">
         <v>350</v>

--- a/F3M_FP&A_assessment_ready_AI_v1.xlsx
+++ b/F3M_FP&A_assessment_ready_AI_v1.xlsx
@@ -330,7 +330,7 @@
     <t>Dashboards integrados, autoservicio controlado, drill-down y conexión con acciones de gestión.</t>
   </si>
   <si>
-    <t>Visualización ejecutiva avanzada, con insights automáticos, alertas, narrativa analítica y soporte predictivo.</t>
+    <t>Visualización ejecutiva avanzada, con conclusiones automáticas, alertas, narrativa analítica y soporte predictivo.</t>
   </si>
   <si>
     <t>¿Existen dashboards por nivel directivo?
@@ -399,7 +399,7 @@
     <t>Metodología integrada con escenarios, sensibilidad, dependencias, beneficios no financieros y gobierno de aprobación.</t>
   </si>
   <si>
-    <t>Gestión portfolio basada en valor, con priorización dinámica, tracking de beneficios y aprendizaje post-implementación.</t>
+    <t>Gestión de la cartera de iniciativas basada en valor, con priorización dinámica, seguimiento de beneficios y aprendizaje posterior a la implantación.</t>
   </si>
   <si>
     <t>¿Existe plantilla estándar?
@@ -534,7 +534,7 @@
     <t>Información integrada, trazable, orientada a decisión y conectada con análisis de escenarios.</t>
   </si>
   <si>
-    <t>Decision intelligence con insights predictivos, recomendaciones y autoservicio gobernado para la dirección.</t>
+    <t>Inteligencia de decisión con conclusiones predictivas, recomendaciones y autoservicio analítico gobernado para la dirección.</t>
   </si>
   <si>
     <t>¿Qué decisiones soporta FP&amp;A?
@@ -633,7 +633,7 @@
     <t>Storytelling financiero integrado con dashboards, escenarios, decisiones requeridas y seguimiento.</t>
   </si>
   <si>
-    <t>Narrativa ejecutiva dinámica, basada en insights automáticos, anticipación de riesgos y recomendaciones de decisión.</t>
+    <t>Narrativa ejecutiva dinámica, basada en conclusiones automáticas, anticipación de riesgos y recomendaciones de decisión.</t>
   </si>
   <si>
     <t>¿Los informes incluyen mensajes ejecutivos?
@@ -735,7 +735,7 @@
     <t>Conexión integrada entre estrategia, capital allocation, presupuesto, forecast y performance management.</t>
   </si>
   <si>
-    <t>Modelo cerrado estrategia-ejecución-aprendizaje, con feedback continuo, reasignación dinámica y gestión del portfolio de iniciativas.</t>
+    <t>Modelo cerrado de estrategia, ejecución y aprendizaje, con retroalimentación continua, reasignación dinámica y gestión de la cartera de iniciativas.</t>
   </si>
   <si>
     <t>¿La estrategia se traduce en objetivos financieros?

--- a/F3M_FP&A_assessment_ready_AI_v1.xlsx
+++ b/F3M_FP&A_assessment_ready_AI_v1.xlsx
@@ -140,7 +140,7 @@
     <t>Calendario presupuestario; RACI; workflow de aprobación; plantillas; actas de comités; control de versiones.</t>
   </si>
   <si>
-    <t>Diseñar modelo de gobierno FP&amp;A con calendario integrado, RACI, workflow de aprobación, criterios comunes y control de versiones.</t>
+    <t>Diseñar modelo de gobierno FP&amp;A con calendario integrado, RACI, flujo de aprobación, criterios comunes y control de versiones.</t>
   </si>
   <si>
     <t>1.2 Modelo presupuestario y drivers de planificación</t>
@@ -173,7 +173,7 @@
     <t>Catálogo de drivers; modelo de planificación; documentación de supuestos; análisis de sensibilidad; inputs operativos.</t>
   </si>
   <si>
-    <t>Evolucionar hacia un modelo driver-based planning con catálogo de drivers, reglas de cálculo, trazabilidad y análisis de sensibilidad.</t>
+    <t>Evolucionar hacia una planificación basada en drivers, con catálogo de drivers, reglas de cálculo, trazabilidad y análisis de sensibilidad.</t>
   </si>
   <si>
     <t>1.3 Integración de escenarios y rolling forecast</t>
@@ -207,7 +207,7 @@
     <t>Modelos de forecast; supuestos; escenarios; calendario de reforecast; reporting de desviaciones; alertas.</t>
   </si>
   <si>
-    <t>Implantar rolling forecast con escenarios base/optimista/pesimista, supuestos documentados y automatización de inputs críticos.</t>
+    <t>Implantar previsión continua (rolling forecast) con escenarios base, optimista y pesimista, supuestos documentados y automatización de los datos de entrada críticos.</t>
   </si>
   <si>
     <t>1.4 Colaboración y accountability presupuestaria</t>
@@ -240,7 +240,7 @@
     <t>RACI; workflows; aprobaciones; trazabilidad de cambios; actas de challenge; seguimiento de compromisos.</t>
   </si>
   <si>
-    <t>Definir ownership presupuestario por dimensión/unidad, con workflow colaborativo, challenge financiero y seguimiento de compromisos.</t>
+    <t>Definir la responsabilidad presupuestaria por dimensión y unidad, con flujo colaborativo, contraste financiero y seguimiento de compromisos.</t>
   </si>
   <si>
     <t>Informes de gestión del rendimiento</t>
@@ -276,7 +276,7 @@
     <t>Catálogo de KPIs; paquetes de reporting; dashboards; actas de revisión; planes de acción.</t>
   </si>
   <si>
-    <t>Rediseñar el reporting de gestión alrededor de objetivos, KPIs, desviaciones, causas, owners y acciones.</t>
+    <t>Rediseñar los informes de gestión alrededor de objetivos, KPIs, desviaciones, causas, responsables y acciones.</t>
   </si>
   <si>
     <t>2.2 Análisis de desviaciones y causa-raíz</t>
@@ -309,7 +309,7 @@
     <t>Reportes de desviaciones; árboles de drivers; actas con acciones; forecast actualizado; dashboards.</t>
   </si>
   <si>
-    <t>Crear metodología de variance analysis por driver, dimensión, owner, causa-raíz, acción y seguimiento.</t>
+    <t>Crear metodología de análisis de desviaciones por driver, dimensión, responsable, causa-raíz, acción y seguimiento.</t>
   </si>
   <si>
     <t>2.3 Cuadros de mando y visualización ejecutiva</t>
@@ -342,7 +342,7 @@
     <t>Dashboards; modelo semántico; guía de KPIs; evidencias de automatización; accesos por perfil.</t>
   </si>
   <si>
-    <t>Implantar cuadro de mando FP&amp;A con KPIs homologados, drill-down, acceso por perfil y automatización de datos.</t>
+    <t>Implantar cuadro de mando FP&amp;A con KPIs homologados, navegación al detalle, acceso por perfil y automatización de datos.</t>
   </si>
   <si>
     <t>2.4 Rutinas de performance y toma de acciones</t>
@@ -375,7 +375,7 @@
     <t>Calendario de comités; actas; trackers de acciones; KPIs de impacto; reportes de seguimiento.</t>
   </si>
   <si>
-    <t>Formalizar rutinas de performance con agenda estándar, tracker de acciones, owners, beneficios esperados y seguimiento.</t>
+    <t>Formalizar rutinas de revisión del rendimiento con agenda estándar, registro de acciones, responsables, beneficios esperados y seguimiento.</t>
   </si>
   <si>
     <t>Evaluación business case</t>
@@ -444,7 +444,7 @@
     <t>Modelos financieros; bibliotecas de supuestos; análisis de sensibilidad; outputs de comité; documentación metodológica.</t>
   </si>
   <si>
-    <t>Construir modelo financiero estándar para iniciativas con P&amp;L, cash, balance, sensibilidad, escenarios y trazabilidad de supuestos.</t>
+    <t>Construir modelo financiero estándar para iniciativas con cuenta de resultados, caja, balance, sensibilidad, escenarios y trazabilidad de supuestos.</t>
   </si>
   <si>
     <t>3.3 Priorización y asignación de capital</t>
@@ -510,7 +510,7 @@
     <t>Benefit tracker; informes post-implementación; actas de revisión; acciones correctivas; repositorio de aprendizajes.</t>
   </si>
   <si>
-    <t>Implantar benefit tracking con owners, métricas, línea base, seguimiento periódico y revisión post-implementación.</t>
+    <t>Implantar seguimiento de beneficios con responsables, métricas, línea base, revisiones periódicas y revisión posterior a la implantación.</t>
   </si>
   <si>
     <t>Información y apoyo a la toma de decisiones</t>
@@ -579,7 +579,7 @@
     <t>Modelos de escenarios; análisis de sensibilidad; documentación de supuestos; dashboards; outputs de comités.</t>
   </si>
   <si>
-    <t>Crear framework de análisis de escenarios para decisiones clave, con drivers, impactos, sensibilidad y recomendaciones.</t>
+    <t>Crear marco de análisis de escenarios para decisiones clave, con drivers, impactos, sensibilidad y recomendaciones.</t>
   </si>
   <si>
     <t>4.3 Finance business partnering y challenge al negocio</t>
@@ -612,7 +612,7 @@
     <t>Modelo organizativo; RACI; agendas de comités; actas de decisiones; objetivos de business partnering; feedback del negocio.</t>
   </si>
   <si>
-    <t>Definir modelo de finance business partnering con roles, responsabilidades, foros de decisión, capacidades requeridas y métricas de valor.</t>
+    <t>Definir modelo de Finanzas como socio del negocio (business partnering) con roles, responsabilidades, foros de decisión, capacidades requeridas y métricas de valor.</t>
   </si>
   <si>
     <t>4.4 Narrativa financiera y comunicación ejecutiva</t>
@@ -714,7 +714,7 @@
     <t>Modelos de escenarios; stress tests; supuestos macro/operativos; planes de contingencia; actas de comité.</t>
   </si>
   <si>
-    <t>Crear metodología de escenarios estratégicos y stress testing con variables clave, impactos financieros y planes de respuesta.</t>
+    <t>Crear metodología de escenarios estratégicos y pruebas de estrés con variables clave, impactos financieros y planes de respuesta.</t>
   </si>
   <si>
     <t>5.3 Conexión entre estrategia, presupuesto y ejecución</t>
@@ -747,7 +747,7 @@
     <t>Mapa estratégico; KPIs; presupuesto por iniciativas; portfolio; comités de seguimiento; roadmap estratégico.</t>
   </si>
   <si>
-    <t>Diseñar puente estrategia-presupuesto-ejecución con objetivos financieros, iniciativas, KPIs, owners y seguimiento de recursos.</t>
+    <t>Diseñar puente estrategia-presupuesto-ejecución con objetivos financieros, iniciativas, KPIs, responsables y seguimiento de recursos.</t>
   </si>
   <si>
     <t>5.4 Seguimiento de creación de valor a largo plazo</t>
@@ -780,7 +780,7 @@
     <t>KPIs de valor; benefit tracking estratégico; reportes de plan; actas de comité; decisiones de reasignación.</t>
   </si>
   <si>
-    <t>Implantar modelo de seguimiento de creación de valor con KPIs, beneficios, riesgos, owners y revisión periódica de asignación de recursos.</t>
+    <t>Implantar modelo de seguimiento de creación de valor con KPIs, beneficios, riesgos, responsables y revisión periódica de asignación de recursos.</t>
   </si>
   <si>
     <t>Score global dominio</t>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="E2" s="1" t="str">
         <f>Assessment!R2</f>
-        <v>Diseñar modelo de gobierno FP&amp;A con calendario integrado, RACI, workflow de aprobación, criterios comunes y control de versiones.</v>
+        <v>Diseñar modelo de gobierno FP&amp;A con calendario integrado, RACI, flujo de aprobación, criterios comunes y control de versiones.</v>
       </c>
       <c r="F2" s="1" t="str">
         <f t="shared" ref="F2:F21" si="0">IF(D2="Alta","Oleada 1",IF(D2="Media","Oleada 2","Oleada 3"))</f>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="E3" s="1" t="str">
         <f>Assessment!R3</f>
-        <v>Evolucionar hacia un modelo driver-based planning con catálogo de drivers, reglas de cálculo, trazabilidad y análisis de sensibilidad.</v>
+        <v>Evolucionar hacia una planificación basada en drivers, con catálogo de drivers, reglas de cálculo, trazabilidad y análisis de sensibilidad.</v>
       </c>
       <c r="F3" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="E4" s="1" t="str">
         <f>Assessment!R4</f>
-        <v>Implantar rolling forecast con escenarios base/optimista/pesimista, supuestos documentados y automatización de inputs críticos.</v>
+        <v>Implantar previsión continua (rolling forecast) con escenarios base, optimista y pesimista, supuestos documentados y automatización de los datos de entrada críticos.</v>
       </c>
       <c r="F4" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="E5" s="1" t="str">
         <f>Assessment!R5</f>
-        <v>Definir ownership presupuestario por dimensión/unidad, con workflow colaborativo, challenge financiero y seguimiento de compromisos.</v>
+        <v>Definir la responsabilidad presupuestaria por dimensión y unidad, con flujo colaborativo, contraste financiero y seguimiento de compromisos.</v>
       </c>
       <c r="F5" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E6" s="1" t="str">
         <f>Assessment!R6</f>
-        <v>Rediseñar el reporting de gestión alrededor de objetivos, KPIs, desviaciones, causas, owners y acciones.</v>
+        <v>Rediseñar los informes de gestión alrededor de objetivos, KPIs, desviaciones, causas, responsables y acciones.</v>
       </c>
       <c r="F6" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="E7" s="1" t="str">
         <f>Assessment!R7</f>
-        <v>Crear metodología de variance analysis por driver, dimensión, owner, causa-raíz, acción y seguimiento.</v>
+        <v>Crear metodología de análisis de desviaciones por driver, dimensión, responsable, causa-raíz, acción y seguimiento.</v>
       </c>
       <c r="F7" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="E8" s="1" t="str">
         <f>Assessment!R8</f>
-        <v>Implantar cuadro de mando FP&amp;A con KPIs homologados, drill-down, acceso por perfil y automatización de datos.</v>
+        <v>Implantar cuadro de mando FP&amp;A con KPIs homologados, navegación al detalle, acceso por perfil y automatización de datos.</v>
       </c>
       <c r="F8" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="E9" s="1" t="str">
         <f>Assessment!R9</f>
-        <v>Formalizar rutinas de performance con agenda estándar, tracker de acciones, owners, beneficios esperados y seguimiento.</v>
+        <v>Formalizar rutinas de revisión del rendimiento con agenda estándar, registro de acciones, responsables, beneficios esperados y seguimiento.</v>
       </c>
       <c r="F9" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="E11" s="1" t="str">
         <f>Assessment!R11</f>
-        <v>Construir modelo financiero estándar para iniciativas con P&amp;L, cash, balance, sensibilidad, escenarios y trazabilidad de supuestos.</v>
+        <v>Construir modelo financiero estándar para iniciativas con cuenta de resultados, caja, balance, sensibilidad, escenarios y trazabilidad de supuestos.</v>
       </c>
       <c r="F11" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="E13" s="1" t="str">
         <f>Assessment!R13</f>
-        <v>Implantar benefit tracking con owners, métricas, línea base, seguimiento periódico y revisión post-implementación.</v>
+        <v>Implantar seguimiento de beneficios con responsables, métricas, línea base, revisiones periódicas y revisión posterior a la implantación.</v>
       </c>
       <c r="F13" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E15" s="1" t="str">
         <f>Assessment!R15</f>
-        <v>Crear framework de análisis de escenarios para decisiones clave, con drivers, impactos, sensibilidad y recomendaciones.</v>
+        <v>Crear marco de análisis de escenarios para decisiones clave, con drivers, impactos, sensibilidad y recomendaciones.</v>
       </c>
       <c r="F15" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="E16" s="1" t="str">
         <f>Assessment!R16</f>
-        <v>Definir modelo de finance business partnering con roles, responsabilidades, foros de decisión, capacidades requeridas y métricas de valor.</v>
+        <v>Definir modelo de Finanzas como socio del negocio (business partnering) con roles, responsabilidades, foros de decisión, capacidades requeridas y métricas de valor.</v>
       </c>
       <c r="F16" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="E19" s="1" t="str">
         <f>Assessment!R19</f>
-        <v>Crear metodología de escenarios estratégicos y stress testing con variables clave, impactos financieros y planes de respuesta.</v>
+        <v>Crear metodología de escenarios estratégicos y pruebas de estrés con variables clave, impactos financieros y planes de respuesta.</v>
       </c>
       <c r="F19" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="E20" s="1" t="str">
         <f>Assessment!R20</f>
-        <v>Diseñar puente estrategia-presupuesto-ejecución con objetivos financieros, iniciativas, KPIs, owners y seguimiento de recursos.</v>
+        <v>Diseñar puente estrategia-presupuesto-ejecución con objetivos financieros, iniciativas, KPIs, responsables y seguimiento de recursos.</v>
       </c>
       <c r="F20" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="E21" s="1" t="str">
         <f>Assessment!R21</f>
-        <v>Implantar modelo de seguimiento de creación de valor con KPIs, beneficios, riesgos, owners y revisión periódica de asignación de recursos.</v>
+        <v>Implantar modelo de seguimiento de creación de valor con KPIs, beneficios, riesgos, responsables y revisión periódica de asignación de recursos.</v>
       </c>
       <c r="F21" s="1" t="str">
         <f t="shared" si="0"/>
